--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>112684970</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121143098</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -843,11 +843,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -955,11 +951,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>112684970</v>
       </c>
       <c r="B3" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>121143098</v>
       </c>
       <c r="B4" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
